--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_193_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_193_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M2" t="n">
         <v>16</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
+        <v>11</v>
+      </c>
+      <c r="K3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" t="n">
         <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,10 +1335,10 @@
         <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
@@ -2903,16 +2903,16 @@
         <v>17</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>2</v>
@@ -3102,13 +3102,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X26" t="n">
         <v>12</v>
@@ -3497,10 +3497,10 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>2</v>
@@ -3827,16 +3827,16 @@
         <v>110</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -4292,7 +4292,7 @@
         <v>13</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4488,10 +4488,10 @@
         <v>22</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4880,10 +4880,10 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5272,10 +5272,10 @@
         <v>5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>1</v>
@@ -5667,13 +5667,13 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
         <v>4</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>97</v>
       </c>
       <c r="T48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U48" t="n">
+        <v>15</v>
+      </c>
+      <c r="V48" t="n">
         <v>3</v>
       </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X48" t="n">
         <v>28</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_193_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_193_EL.xlsx
@@ -674,10 +674,10 @@
         <v>16</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>65.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2523,10 +2523,10 @@
         <v>2</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
         <v>2</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>9</v>
       </c>
       <c r="X30" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Y30" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4892,10 +4892,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,14 +5676,14 @@
         <v>2</v>
       </c>
       <c r="X42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6264,14 +6264,14 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y45" t="n">
         <v>3</v>
       </c>
-      <c r="Y45" t="n">
-        <v>4</v>
-      </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6796,14 +6796,14 @@
         <v>3</v>
       </c>
       <c r="X48" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="Y48" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="AA48" t="n">
